--- a/artfynd/A 69612-2021 artfynd.xlsx
+++ b/artfynd/A 69612-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 69612-2021 artfynd.xlsx
+++ b/artfynd/A 69612-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,64 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>112299152</v>
+        <v>86978342</v>
       </c>
       <c r="B2" t="n">
-        <v>90210</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97367</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6031</v>
+        <v>291</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Stubbtrådmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Fuscocephaloziopsis catenulata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+          <t>(Huebener) Váňa &amp; L.Söderstr.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Storhultet, Srm</t>
+          <t>Stora hultet, Srm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>618101</v>
+        <v>618047</v>
       </c>
       <c r="R2" t="n">
-        <v>6523518</v>
+        <v>6523359</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -756,12 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-09-24</t>
+          <t>2020-06-30</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-09-24</t>
+          <t>2020-06-30</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -770,10 +754,14 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>låga i skogen</t>
+        </is>
+      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
@@ -786,6 +774,215 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>73717656</v>
+      </c>
+      <c r="B3" t="n">
+        <v>93233</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Storhultet 4, Srm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>618080</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6523314</v>
+      </c>
+      <c r="S3" t="n">
+        <v>25</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Nyköping</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Svärta</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2018-10-17</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2018-10-17</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Gunilla Björkhem</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Gunilla Björkhem</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>112299152</v>
+      </c>
+      <c r="B4" t="n">
+        <v>92567</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>6031</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Blomkålssvamp</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Sparassis crispa</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Wulfen:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Storhultet, Srm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>618101</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6523519</v>
+      </c>
+      <c r="S4" t="n">
+        <v>50</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Nyköping</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Svärta</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2023-09-24</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2023-09-24</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Kristoffer Hylander</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Kristoffer Hylander</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 69612-2021 artfynd.xlsx
+++ b/artfynd/A 69612-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86978342</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73717656</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -983,8 +998,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112299152</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>